--- a/Projects/Prooject_Teams.xlsx
+++ b/Projects/Prooject_Teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BEB819D-C2A9-4D5E-8389-61D900138E33}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F72331-F3D2-4B18-8E95-2370E83B22F1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{CFFCAC46-098C-4A9A-8C1A-17A7E0413977}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -279,13 +279,22 @@
     <t>570816</t>
   </si>
   <si>
-    <t>570</t>
-  </si>
-  <si>
     <t>Team #</t>
   </si>
   <si>
     <t>Project Title</t>
+  </si>
+  <si>
+    <t>Hello world</t>
+  </si>
+  <si>
+    <t>Online Auction</t>
+  </si>
+  <si>
+    <t>570838</t>
+  </si>
+  <si>
+    <t>Wecation</t>
   </si>
 </sst>
 </file>
@@ -316,7 +325,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -365,8 +374,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -389,11 +404,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
@@ -410,8 +462,43 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -726,28 +813,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5048DADC-C0B1-46EA-9E7A-D15BB80A3978}">
-  <dimension ref="B2:H43"/>
+  <dimension ref="B2:E43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
@@ -757,8 +845,11 @@
       <c r="D3" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E3" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
@@ -768,8 +859,9 @@
       <c r="D4" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E4" s="25"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
@@ -779,8 +871,9 @@
       <c r="D5" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E5" s="25"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -790,9 +883,9 @@
       <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="H6" s="16"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>76</v>
       </c>
@@ -802,8 +895,9 @@
       <c r="D7" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E7" s="25"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
@@ -813,8 +907,11 @@
       <c r="D8" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E8" s="23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>40</v>
       </c>
@@ -824,8 +921,9 @@
       <c r="D9" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>46</v>
       </c>
@@ -835,8 +933,9 @@
       <c r="D10" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E10" s="23"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>58</v>
       </c>
@@ -846,8 +945,9 @@
       <c r="D11" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E11" s="23"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>26</v>
       </c>
@@ -857,8 +957,9 @@
       <c r="D12" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E12" s="23"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>60</v>
       </c>
@@ -868,8 +969,9 @@
       <c r="D13" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>16</v>
       </c>
@@ -879,8 +981,11 @@
       <c r="D14" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E14" s="24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>22</v>
       </c>
@@ -890,8 +995,9 @@
       <c r="D15" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E15" s="24"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
         <v>24</v>
       </c>
@@ -901,8 +1007,9 @@
       <c r="D16" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="24"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>62</v>
       </c>
@@ -912,8 +1019,9 @@
       <c r="D17" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="24"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>68</v>
       </c>
@@ -923,8 +1031,9 @@
       <c r="D18" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="24"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="s">
         <v>20</v>
       </c>
@@ -934,8 +1043,9 @@
       <c r="D19" s="9">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="26"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>4</v>
       </c>
@@ -945,8 +1055,9 @@
       <c r="D20" s="9">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="26"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>48</v>
       </c>
@@ -956,8 +1067,9 @@
       <c r="D21" s="9">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="26"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>50</v>
       </c>
@@ -967,8 +1079,9 @@
       <c r="D22" s="9">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="26"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>56</v>
       </c>
@@ -978,8 +1091,9 @@
       <c r="D23" s="9">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="26"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="10" t="s">
         <v>28</v>
       </c>
@@ -989,8 +1103,9 @@
       <c r="D24" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="27"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="10" t="s">
         <v>32</v>
       </c>
@@ -1000,8 +1115,9 @@
       <c r="D25" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E25" s="27"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="10" t="s">
         <v>66</v>
       </c>
@@ -1011,8 +1127,9 @@
       <c r="D26" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E26" s="27"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="10" t="s">
         <v>72</v>
       </c>
@@ -1022,8 +1139,9 @@
       <c r="D27" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E27" s="27"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="10" t="s">
         <v>74</v>
       </c>
@@ -1033,8 +1151,9 @@
       <c r="D28" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E28" s="27"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="12" t="s">
         <v>6</v>
       </c>
@@ -1044,8 +1163,9 @@
       <c r="D29" s="13">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E29" s="28"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="12" t="s">
         <v>8</v>
       </c>
@@ -1055,8 +1175,9 @@
       <c r="D30" s="13">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E30" s="28"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="12" t="s">
         <v>42</v>
       </c>
@@ -1066,8 +1187,9 @@
       <c r="D31" s="13">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E31" s="28"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="12" t="s">
         <v>38</v>
       </c>
@@ -1077,8 +1199,9 @@
       <c r="D32" s="13">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E32" s="28"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
         <v>82</v>
       </c>
@@ -1088,8 +1211,9 @@
       <c r="D33" s="13">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E33" s="28"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>10</v>
       </c>
@@ -1099,8 +1223,9 @@
       <c r="D34" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E34" s="17"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>36</v>
       </c>
@@ -1110,8 +1235,9 @@
       <c r="D35" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E35" s="18"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>44</v>
       </c>
@@ -1121,8 +1247,9 @@
       <c r="D36" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E36" s="18"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>54</v>
       </c>
@@ -1132,10 +1259,11 @@
       <c r="D37" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E37" s="18"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>80</v>
@@ -1143,8 +1271,9 @@
       <c r="D38" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="14" t="s">
         <v>30</v>
       </c>
@@ -1154,8 +1283,9 @@
       <c r="D39" s="15">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E39" s="20"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="14" t="s">
         <v>34</v>
       </c>
@@ -1165,8 +1295,9 @@
       <c r="D40" s="15">
         <v>8</v>
       </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E40" s="21"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="14" t="s">
         <v>52</v>
       </c>
@@ -1176,8 +1307,9 @@
       <c r="D41" s="15">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E41" s="21"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="14" t="s">
         <v>70</v>
       </c>
@@ -1187,8 +1319,9 @@
       <c r="D42" s="15">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E42" s="21"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="14" t="s">
         <v>78</v>
       </c>
@@ -1198,11 +1331,22 @@
       <c r="D43" s="15">
         <v>8</v>
       </c>
+      <c r="E43" s="22"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D47">
     <sortCondition ref="D3:D47"/>
   </sortState>
+  <mergeCells count="8">
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E18"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="E19:E23"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="E29:E33"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Projects/Prooject_Teams.xlsx
+++ b/Projects/Prooject_Teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F72331-F3D2-4B18-8E95-2370E83B22F1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6B5803-315D-4CCF-9983-CB15A1C74165}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{CFFCAC46-098C-4A9A-8C1A-17A7E0413977}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -295,6 +295,21 @@
   </si>
   <si>
     <t>Wecation</t>
+  </si>
+  <si>
+    <t>Meditrack</t>
+  </si>
+  <si>
+    <t>Hotel Management</t>
+  </si>
+  <si>
+    <t>Smart Ride</t>
+  </si>
+  <si>
+    <t>PetConnect</t>
+  </si>
+  <si>
+    <t>Finsync</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1058,9 @@
       <c r="D19" s="9">
         <v>4</v>
       </c>
-      <c r="E19" s="26"/>
+      <c r="E19" s="26" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
@@ -1103,7 +1120,9 @@
       <c r="D24" s="11">
         <v>5</v>
       </c>
-      <c r="E24" s="27"/>
+      <c r="E24" s="27" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="10" t="s">
@@ -1163,7 +1182,9 @@
       <c r="D29" s="13">
         <v>6</v>
       </c>
-      <c r="E29" s="28"/>
+      <c r="E29" s="28" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="12" t="s">
@@ -1223,7 +1244,9 @@
       <c r="D34" s="5">
         <v>7</v>
       </c>
-      <c r="E34" s="17"/>
+      <c r="E34" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
@@ -1283,7 +1306,9 @@
       <c r="D39" s="15">
         <v>8</v>
       </c>
-      <c r="E39" s="20"/>
+      <c r="E39" s="20" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="14" t="s">
